--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\Code\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF0A679-B270-4A7A-AFFB-6BB9E9A08CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833FB0E0-F8C2-4933-A959-189C6DFD0456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="11">
   <si>
     <t>Time</t>
   </si>
@@ -89,13 +89,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,12 +534,6 @@
       <c r="A6" s="1">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
@@ -561,12 +554,6 @@
       <c r="A7" s="1">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
@@ -587,12 +574,6 @@
       <c r="A8" s="1">
         <v>0.5</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -613,12 +594,6 @@
       <c r="A9" s="1">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
@@ -639,12 +614,6 @@
       <c r="A10" s="1">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
@@ -665,12 +634,6 @@
       <c r="A11" s="1">
         <v>0.625</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
@@ -691,12 +654,6 @@
       <c r="A12" s="1">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
@@ -717,12 +674,6 @@
       <c r="A13" s="1">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
@@ -743,12 +694,6 @@
       <c r="A14" s="1">
         <v>0.75</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
@@ -769,12 +714,6 @@
       <c r="A15" s="1">
         <v>0.79166666666666663</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
@@ -795,12 +734,6 @@
       <c r="A16" s="1">
         <v>0.83333333333333337</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
@@ -821,12 +754,6 @@
       <c r="A17" s="1">
         <v>0.875</v>
       </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
@@ -846,12 +773,6 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>0.91666666666666663</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
@@ -1057,13 +978,11 @@
       <c r="A12" s="1">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
